--- a/summary.xlsx
+++ b/summary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
   <si>
     <t>Date</t>
   </si>
@@ -57,6 +57,15 @@
   </si>
   <si>
     <t>knowledge transfer session with Prachi on ViewComponent implementation and usage.</t>
+  </si>
+  <si>
+    <t>In HRMS, find pending employee who are yet to claim reimbursement of the medical expenses and mail it to the account team. It is requested by Laxmi Madam from accounts team.</t>
+  </si>
+  <si>
+    <t>Front-end integration of maker and checker activity.</t>
+  </si>
+  <si>
+    <t>Knowledge Transfer to Iram and Viswaja regarding Alternate Authority implementation in ACE application.</t>
   </si>
 </sst>
 </file>
@@ -459,13 +468,37 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
+      <c r="A7" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
+      <c r="A8" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
+      <c r="A9" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="22">
   <si>
     <t>Date</t>
   </si>
@@ -66,6 +66,30 @@
   </si>
   <si>
     <t>Knowledge Transfer to Iram and Viswaja regarding Alternate Authority implementation in ACE application.</t>
+  </si>
+  <si>
+    <t>Procedure and API creation for ACE application in HRMS.</t>
+  </si>
+  <si>
+    <t>Working on the editing, send to checker and corrsoponding status modification of a project. Also simultaniously creating preview of what has actually changed in the file.</t>
+  </si>
+  <si>
+    <t>Working on Creting batch when a batch has ended its life cycle.</t>
+  </si>
+  <si>
+    <t>Brainstorming with ACE team for creataion, consumption and implementation of newly ceated API of HRMS and also asked for An API from them to integrate in Dashboard PendingList.</t>
+  </si>
+  <si>
+    <t>"Send to Checker" and "Checker Action " batch wise has been completed.</t>
+  </si>
+  <si>
+    <t>What has changed by two different version as been developed. When Approver going to take action, a detailed view of changes have been showed to them.</t>
+  </si>
+  <si>
+    <t>Creating new batch on edit after approval,</t>
+  </si>
+  <si>
+    <t>Editing of the existing batch.</t>
   </si>
 </sst>
 </file>
@@ -393,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -501,25 +525,92 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
+      <c r="A10" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
+      <c r="A15" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
+      <c r="A16" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
   <si>
     <t>Date</t>
   </si>
@@ -90,6 +90,36 @@
   </si>
   <si>
     <t>Editing of the existing batch.</t>
+  </si>
+  <si>
+    <t>Creating new batch on edit after approval</t>
+  </si>
+  <si>
+    <t>Fixed error on creation of new project after introducing batch</t>
+  </si>
+  <si>
+    <t>Created New API for ACE, Provide All activated Alternate authority and respective Authorities on whoes behalf they are acting as alternate.</t>
+  </si>
+  <si>
+    <t>Display project details of any version in IPMS . It will highlight differences from there last version.</t>
+  </si>
+  <si>
+    <t>Project review meeting of IPMS has been done.</t>
+  </si>
+  <si>
+    <t>1. Registration Start Date and End date should be captured.</t>
+  </si>
+  <si>
+    <t>2. CR meeting on 19-11-2025, will be scheduled.</t>
+  </si>
+  <si>
+    <t>3. We are not going to include RPG , right now. It will be discussed later.</t>
+  </si>
+  <si>
+    <t>4. Decision will be gathered from CR about when Project will be finalise i.e when application barred user to modify details. On finalise we will build our master database for future references.</t>
+  </si>
+  <si>
+    <t>Provide help in ACE Enhancement also in Payroll Projection.</t>
   </si>
 </sst>
 </file>
@@ -417,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -612,6 +642,116 @@
         <v>21</v>
       </c>
     </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="41">
   <si>
     <t>Date</t>
   </si>
@@ -120,6 +120,33 @@
   </si>
   <si>
     <t>Provide help in ACE Enhancement also in Payroll Projection.</t>
+  </si>
+  <si>
+    <t>Provide solution for swipe mismatch change request, raised on 14-11-2025, by HR/Admin.</t>
+  </si>
+  <si>
+    <t>Modifying API as per recruirement from ACE.</t>
+  </si>
+  <si>
+    <t>Make provision to show Pending list of ACE application in HRMS dashboard pop-up window. API should be given by ACE team.</t>
+  </si>
+  <si>
+    <t>HRMS Branch marging, Procedure and table column transfer from Dev To Prod Server, and publishing of HRMS.</t>
+  </si>
+  <si>
+    <t>Fixing Redirection of ACE Application URL in HRMS.</t>
+  </si>
+  <si>
+    <t>Project Number Details and Post and Specialization under Project No modification in IPMS.</t>
+  </si>
+  <si>
+    <t>Fix Redirection of ACE Application URL in HRMS.</t>
+  </si>
+  <si>
+    <t>Fix issues after implementation of ACE pending list in HRMS, in production.</t>
+  </si>
+  <si>
+    <t>Created Logic of CO encashment for tax projection calculation and shared with Prachi.</t>
   </si>
 </sst>
 </file>
@@ -447,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -752,6 +779,116 @@
         <v>31</v>
       </c>
     </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B35" t="s">
+        <v>3</v>
+      </c>
+      <c r="C35" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SAPTARSHI BANERJEE\WORKLOGS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SAPTARSHI BANERJEE\PERSONAL\PROJECT\OTHERS\WORKLOGS\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="58">
   <si>
     <t>Date</t>
   </si>
@@ -147,6 +147,57 @@
   </si>
   <si>
     <t>Created Logic of CO encashment for tax projection calculation and shared with Prachi.</t>
+  </si>
+  <si>
+    <t>Creataion and updation of Project Number Details and Post &amp; Specialization under Project No(s) has been done.</t>
+  </si>
+  <si>
+    <t>Assigning Premament Project numbers.</t>
+  </si>
+  <si>
+    <t>Show modfied details of Project Number, Post and Specializations are going on.</t>
+  </si>
+  <si>
+    <t>IPMS meeting with CR was held on 19th Novermebr, 2025. Following points are highlight of the discussion during the presentation.</t>
+  </si>
+  <si>
+    <t>In the detail view, they suggested to show version number along with checker name and date.</t>
+  </si>
+  <si>
+    <t>Asked for a non-editable Description field at the time of project initiation.</t>
+  </si>
+  <si>
+    <t>They asked for a specific header like Initial Project or Revised Project, along with revision date and approver name, to indicate the project status.</t>
+  </si>
+  <si>
+    <t>They have a requirement of trail mail configuration in the application; i.e., when a mail is triggered after the first time, it should contain all previous emails of the project.</t>
+  </si>
+  <si>
+    <t>In the next patch, we propose to provide the following:</t>
+  </si>
+  <si>
+    <t>Project numbers with post and specialization details entry.</t>
+  </si>
+  <si>
+    <t>Assign permanent project numbers.</t>
+  </si>
+  <si>
+    <t>Configure email recipients (to whom the email will be triggered).</t>
+  </si>
+  <si>
+    <t>Send email for specific mention, if required, to groups or individuals.</t>
+  </si>
+  <si>
+    <t>Accommodate user-category-wise login for visualization of flow of data.</t>
+  </si>
+  <si>
+    <t>Also try to integrate full project details rendered as view.</t>
+  </si>
+  <si>
+    <t>🚧 Blockers</t>
+  </si>
+  <si>
+    <t>Increasing and Decreasing of Project number in initial configuration , will create problems. Need to fix the area.</t>
   </si>
 </sst>
 </file>
@@ -474,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -889,6 +940,182 @@
         <v>37</v>
       </c>
     </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B38" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B42" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B43" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B45" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B47" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B48" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B52" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B53" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="58">
   <si>
     <t>Date</t>
   </si>
@@ -525,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -1116,6 +1116,182 @@
         <v>57</v>
       </c>
     </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B54" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B55" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B57" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B58" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B59" t="s">
+        <v>9</v>
+      </c>
+      <c r="C59" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B60" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B61" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B62" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B63" t="s">
+        <v>9</v>
+      </c>
+      <c r="C63" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B64" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B65" t="s">
+        <v>9</v>
+      </c>
+      <c r="C65" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B66" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B67" t="s">
+        <v>9</v>
+      </c>
+      <c r="C67" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B69" t="s">
+        <v>56</v>
+      </c>
+      <c r="C69" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="61">
   <si>
     <t>Date</t>
   </si>
@@ -198,6 +198,15 @@
   </si>
   <si>
     <t>Increasing and Decreasing of Project number in initial configuration , will create problems. Need to fix the area.</t>
+  </si>
+  <si>
+    <t>Provide solution regarding employee retirement issue,</t>
+  </si>
+  <si>
+    <t>In the detail view, CR suggested to show version number along with checker name and date. It is Incorporated.</t>
+  </si>
+  <si>
+    <t>Working on assign Project numbers and confirm projects. Procedure created. evaluating on various cases that may have arises.</t>
   </si>
 </sst>
 </file>
@@ -525,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -1292,6 +1301,39 @@
         <v>57</v>
       </c>
     </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>45985</v>
+      </c>
+      <c r="B70" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>45985</v>
+      </c>
+      <c r="B71" t="s">
+        <v>3</v>
+      </c>
+      <c r="C71" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>45985</v>
+      </c>
+      <c r="B72" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="89">
   <si>
     <t>Date</t>
   </si>
@@ -207,12 +207,99 @@
   </si>
   <si>
     <t>Working on assign Project numbers and confirm projects. Procedure created. evaluating on various cases that may have arises.</t>
+  </si>
+  <si>
+    <t>One Application used by RPG, to decide cut off of SBI/RRB, was not running from Friday. Fixed the issues and make the application live again. Informed Rushikesh to check whether everything is going perfect or not.</t>
+  </si>
+  <si>
+    <t>Medical expenses  Reimbursement claim windows are enabled by system, but email triggered is failed. Manually sending the email to each one and after that fixation of the issues which caused for either email was not triggered  or blank email was triggered.</t>
+  </si>
+  <si>
+    <t>In Alternateauthority module, At present alternate authority list is showing based the grade of authority, as previously said by Administration department. With that logic when admin is going to set alternate of Dipika Madam(In Grade H), In the alternate list Name of Priya Madam (In Grade G) was missing. Patch to the HRMS Module to bring all division Head in the List of Alternate List.</t>
+  </si>
+  <si>
+    <t>Marge main HRMS code with Prachi and resolve conflicts, test and published.</t>
+  </si>
+  <si>
+    <t>Modify procedure of pending list of Employees in Production DB.</t>
+  </si>
+  <si>
+    <t>Found Email sending issues in HRMS Profile from Database Email Profile and bring this to the notice of respective authorities.</t>
+  </si>
+  <si>
+    <t>Issue in HRMS, regarding employees Type changed and grade changed was detected at the time of testing, is solved and published to the live.</t>
+  </si>
+  <si>
+    <t>Provide details of Contractual Employees Salary to the Admin Section , for review purpose.</t>
+  </si>
+  <si>
+    <t>Sendig Email from server will monitor tomorrow with IT team.</t>
+  </si>
+  <si>
+    <t>Add three candidates data, provided by APG group, in UNFAIRMEANS candidate list.</t>
+  </si>
+  <si>
+    <t>Fixation of issue of bulk email triggered. Compliance with solution provided by IT team.</t>
+  </si>
+  <si>
+    <t>Modify Project Initialization API Flow and corrosponding adjustment in database procedure Is in progress.</t>
+  </si>
+  <si>
+    <t>Brainstorming with Prachi , regarding new enhancement of HRMS, requested by Admin. It is regarding Grade Pay Level of Regular Employee and Term and associated consolidated pay of Contractual employees. Admin Suggestion will incorporated by Prachi in HRMS. I help her to understand the logic and database changes regarding development.</t>
+  </si>
+  <si>
+    <t>Address Prachi's query regarding a DB procedure Loan EMI transaction of Loan Module.</t>
+  </si>
+  <si>
+    <t>Created new procedure to insert Loan EMI Transactions into EMI tables. Initially It Recreates all the application prsent in different tables when ever procedure runs. Now I have created another procedure which take application id and loan subtype id and create EMI transaction for only that specific appliaction of that specific loan sub type. It has scope further enhancement whicha has been shared with prachi. Also helped prachi on some regarding some code.</t>
+  </si>
+  <si>
+    <t>Incorporated Window closing information in the mail which triggered during creation of window of medical reimbursement for employees.</t>
+  </si>
+  <si>
+    <t>Solved an issue in HRMS, reported by Joel Sir, regarding Leave and Leave Exception.</t>
+  </si>
+  <si>
+    <t>Created table and procedure for the tbl_final_project_initiation.</t>
+  </si>
+  <si>
+    <t>Modify the batching process of project initiation.</t>
+  </si>
+  <si>
+    <t>Make some field non-editable in project initial config tab.</t>
+  </si>
+  <si>
+    <t>IPMS meeting with CR has been done.</t>
+  </si>
+  <si>
+    <t>Project Numbers with post and specialization details entry.</t>
+  </si>
+  <si>
+    <t>Configure email, i.e. to whom the email will be triggered.</t>
+  </si>
+  <si>
+    <t>Send email to for a specific mention , if required, to specific group of people or individuals.</t>
+  </si>
+  <si>
+    <t>We will try to accomodate user category wise login for visualization of flow</t>
+  </si>
+  <si>
+    <t>Resolve problem in perquisite of the HRR data creation and fetching.</t>
+  </si>
+  <si>
+    <t>Assiging of Project Numbers to the project is going on. Resolve issue with displaying fields to the views.</t>
+  </si>
+  <si>
+    <t>Scheduled meeting with Director Sir and other stakeholders regarding Nominee application, Asset and Liabilities and Payroll.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -253,7 +340,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -534,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C72"/>
+  <dimension ref="A1:C114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -555,782 +642,1244 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>45968</v>
+        <v>45964</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>45968</v>
+        <v>45964</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>45968</v>
+        <v>45964</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>45968</v>
+        <v>45964</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>45968</v>
+        <v>45964</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>45971</v>
+        <v>45964</v>
       </c>
       <c r="B7" t="s">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>45971</v>
+        <v>45964</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>45971</v>
+        <v>45964</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>45972</v>
+        <v>45964</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>45972</v>
+        <v>45965</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>45972</v>
+        <v>45965</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>45972</v>
+        <v>45965</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>45973</v>
+        <v>45965</v>
       </c>
       <c r="B14" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>45973</v>
+        <v>45965</v>
       </c>
       <c r="B15" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>45973</v>
+        <v>45967</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>45973</v>
+        <v>45967</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>45975</v>
+        <v>45967</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>45975</v>
+        <v>45967</v>
       </c>
       <c r="B19" t="s">
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>45975</v>
+        <v>45967</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>45975</v>
+        <v>45967</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>45975</v>
+        <v>45968</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>45975</v>
+        <v>45968</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>45975</v>
+        <v>45968</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>45975</v>
+        <v>45968</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>45975</v>
+        <v>45968</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>45975</v>
+        <v>45971</v>
       </c>
       <c r="B27" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>45978</v>
+        <v>45971</v>
       </c>
       <c r="B28" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>45978</v>
+        <v>45971</v>
       </c>
       <c r="B29" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>45978</v>
+        <v>45972</v>
       </c>
       <c r="B30" t="s">
         <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>45978</v>
+        <v>45972</v>
       </c>
       <c r="B31" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>45978</v>
+        <v>45972</v>
       </c>
       <c r="B32" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C32" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>45978</v>
+        <v>45972</v>
       </c>
       <c r="B33" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C33" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>45979</v>
+        <v>45973</v>
       </c>
       <c r="B34" t="s">
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>45979</v>
+        <v>45973</v>
       </c>
       <c r="B35" t="s">
         <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>45979</v>
+        <v>45973</v>
       </c>
       <c r="B36" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C36" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>45979</v>
+        <v>45973</v>
       </c>
       <c r="B37" t="s">
         <v>7</v>
       </c>
       <c r="C37" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>45981</v>
+        <v>45974</v>
       </c>
       <c r="B38" t="s">
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>45981</v>
+        <v>45975</v>
       </c>
       <c r="B39" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>45981</v>
+        <v>45975</v>
       </c>
       <c r="B40" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>45981</v>
+        <v>45975</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>45981</v>
+        <v>45975</v>
       </c>
       <c r="B42" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C42" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>45981</v>
+        <v>45975</v>
       </c>
       <c r="B43" t="s">
         <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>45981</v>
+        <v>45975</v>
       </c>
       <c r="B44" t="s">
         <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>45981</v>
+        <v>45975</v>
       </c>
       <c r="B45" t="s">
         <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>45981</v>
+        <v>45975</v>
       </c>
       <c r="B46" t="s">
         <v>9</v>
       </c>
       <c r="C46" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>45981</v>
+        <v>45975</v>
       </c>
       <c r="B47" t="s">
         <v>9</v>
       </c>
       <c r="C47" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>45981</v>
+        <v>45975</v>
       </c>
       <c r="B48" t="s">
         <v>9</v>
       </c>
       <c r="C48" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>45981</v>
+        <v>45978</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C49" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>45981</v>
+        <v>45978</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C50" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>45981</v>
+        <v>45978</v>
       </c>
       <c r="B51" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C51" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>45981</v>
+        <v>45978</v>
       </c>
       <c r="B52" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>45981</v>
+        <v>45978</v>
       </c>
       <c r="B53" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C53" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>45981</v>
+        <v>45978</v>
       </c>
       <c r="B54" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>45981</v>
+        <v>45979</v>
       </c>
       <c r="B55" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C55" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>45981</v>
+        <v>45979</v>
       </c>
       <c r="B56" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>45981</v>
+        <v>45979</v>
       </c>
       <c r="B57" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C57" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>45981</v>
+        <v>45979</v>
       </c>
       <c r="B58" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C58" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>45981</v>
+        <v>45980</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C59" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>45981</v>
+        <v>45980</v>
       </c>
       <c r="B60" t="s">
         <v>9</v>
       </c>
       <c r="C60" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <v>45981</v>
+        <v>45980</v>
       </c>
       <c r="B61" t="s">
         <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>45981</v>
+        <v>45980</v>
       </c>
       <c r="B62" t="s">
         <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>45981</v>
+        <v>45980</v>
       </c>
       <c r="B63" t="s">
         <v>9</v>
       </c>
       <c r="C63" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>45981</v>
+        <v>45980</v>
       </c>
       <c r="B64" t="s">
         <v>9</v>
       </c>
       <c r="C64" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>45981</v>
+        <v>45980</v>
       </c>
       <c r="B65" t="s">
         <v>9</v>
       </c>
       <c r="C65" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>45981</v>
+        <v>45980</v>
       </c>
       <c r="B66" t="s">
         <v>9</v>
       </c>
       <c r="C66" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
-        <v>45981</v>
+        <v>45980</v>
       </c>
       <c r="B67" t="s">
         <v>9</v>
       </c>
       <c r="C67" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>45981</v>
+        <v>45980</v>
       </c>
       <c r="B68" t="s">
         <v>9</v>
       </c>
       <c r="C68" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
-        <v>45981</v>
+        <v>45980</v>
       </c>
       <c r="B69" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="C69" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <v>45985</v>
+        <v>45980</v>
       </c>
       <c r="B70" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
-        <v>45985</v>
+        <v>45980</v>
       </c>
       <c r="B71" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C71" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B72" t="s">
+        <v>56</v>
+      </c>
+      <c r="C72" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B73" t="s">
+        <v>56</v>
+      </c>
+      <c r="C73" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B74" t="s">
+        <v>56</v>
+      </c>
+      <c r="C74" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B75" t="s">
+        <v>56</v>
+      </c>
+      <c r="C75" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B76" t="s">
+        <v>56</v>
+      </c>
+      <c r="C76" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B77" t="s">
+        <v>3</v>
+      </c>
+      <c r="C77" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B78" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B79" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B80" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B81" t="s">
+        <v>9</v>
+      </c>
+      <c r="C81" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B82" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B83" t="s">
+        <v>9</v>
+      </c>
+      <c r="C83" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B84" t="s">
+        <v>9</v>
+      </c>
+      <c r="C84" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B85" t="s">
+        <v>9</v>
+      </c>
+      <c r="C85" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B86" t="s">
+        <v>9</v>
+      </c>
+      <c r="C86" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B87" t="s">
+        <v>9</v>
+      </c>
+      <c r="C87" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B88" t="s">
+        <v>9</v>
+      </c>
+      <c r="C88" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B89" t="s">
+        <v>9</v>
+      </c>
+      <c r="C89" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B90" t="s">
+        <v>9</v>
+      </c>
+      <c r="C90" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B91" t="s">
+        <v>9</v>
+      </c>
+      <c r="C91" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B92" t="s">
+        <v>56</v>
+      </c>
+      <c r="C92" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B93" t="s">
+        <v>3</v>
+      </c>
+      <c r="C93" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B94" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B95" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B96" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B97" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B98" t="s">
+        <v>9</v>
+      </c>
+      <c r="C98" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B99" t="s">
+        <v>9</v>
+      </c>
+      <c r="C99" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B100" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B101" t="s">
+        <v>9</v>
+      </c>
+      <c r="C101" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B102" t="s">
+        <v>9</v>
+      </c>
+      <c r="C102" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B103" t="s">
+        <v>9</v>
+      </c>
+      <c r="C103" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B104" t="s">
+        <v>9</v>
+      </c>
+      <c r="C104" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B105" t="s">
+        <v>9</v>
+      </c>
+      <c r="C105" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B106" t="s">
+        <v>9</v>
+      </c>
+      <c r="C106" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B107" t="s">
+        <v>9</v>
+      </c>
+      <c r="C107" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B108" t="s">
+        <v>56</v>
+      </c>
+      <c r="C108" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B109" t="s">
+        <v>3</v>
+      </c>
+      <c r="C109" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B110" t="s">
+        <v>7</v>
+      </c>
+      <c r="C110" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B111" t="s">
+        <v>9</v>
+      </c>
+      <c r="C111" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="2">
         <v>45985</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B112" t="s">
+        <v>3</v>
+      </c>
+      <c r="C112" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="2">
+        <v>45985</v>
+      </c>
+      <c r="B113" t="s">
+        <v>3</v>
+      </c>
+      <c r="C113" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="2">
+        <v>45985</v>
+      </c>
+      <c r="B114" t="s">
         <v>7</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C114" t="s">
         <v>60</v>
       </c>
     </row>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="71">
   <si>
     <t>Date</t>
   </si>
@@ -104,21 +104,6 @@
     <t>Display project details of any version in IPMS . It will highlight differences from there last version.</t>
   </si>
   <si>
-    <t>Project review meeting of IPMS has been done.</t>
-  </si>
-  <si>
-    <t>1. Registration Start Date and End date should be captured.</t>
-  </si>
-  <si>
-    <t>2. CR meeting on 19-11-2025, will be scheduled.</t>
-  </si>
-  <si>
-    <t>3. We are not going to include RPG , right now. It will be discussed later.</t>
-  </si>
-  <si>
-    <t>4. Decision will be gathered from CR about when Project will be finalise i.e when application barred user to modify details. On finalise we will build our master database for future references.</t>
-  </si>
-  <si>
     <t>Provide help in ACE Enhancement also in Payroll Projection.</t>
   </si>
   <si>
@@ -158,42 +143,6 @@
     <t>Show modfied details of Project Number, Post and Specializations are going on.</t>
   </si>
   <si>
-    <t>IPMS meeting with CR was held on 19th Novermebr, 2025. Following points are highlight of the discussion during the presentation.</t>
-  </si>
-  <si>
-    <t>In the detail view, they suggested to show version number along with checker name and date.</t>
-  </si>
-  <si>
-    <t>Asked for a non-editable Description field at the time of project initiation.</t>
-  </si>
-  <si>
-    <t>They asked for a specific header like Initial Project or Revised Project, along with revision date and approver name, to indicate the project status.</t>
-  </si>
-  <si>
-    <t>They have a requirement of trail mail configuration in the application; i.e., when a mail is triggered after the first time, it should contain all previous emails of the project.</t>
-  </si>
-  <si>
-    <t>In the next patch, we propose to provide the following:</t>
-  </si>
-  <si>
-    <t>Project numbers with post and specialization details entry.</t>
-  </si>
-  <si>
-    <t>Assign permanent project numbers.</t>
-  </si>
-  <si>
-    <t>Configure email recipients (to whom the email will be triggered).</t>
-  </si>
-  <si>
-    <t>Send email for specific mention, if required, to groups or individuals.</t>
-  </si>
-  <si>
-    <t>Accommodate user-category-wise login for visualization of flow of data.</t>
-  </si>
-  <si>
-    <t>Also try to integrate full project details rendered as view.</t>
-  </si>
-  <si>
     <t>🚧 Blockers</t>
   </si>
   <si>
@@ -269,21 +218,6 @@
     <t>Make some field non-editable in project initial config tab.</t>
   </si>
   <si>
-    <t>IPMS meeting with CR has been done.</t>
-  </si>
-  <si>
-    <t>Project Numbers with post and specialization details entry.</t>
-  </si>
-  <si>
-    <t>Configure email, i.e. to whom the email will be triggered.</t>
-  </si>
-  <si>
-    <t>Send email to for a specific mention , if required, to specific group of people or individuals.</t>
-  </si>
-  <si>
-    <t>We will try to accomodate user category wise login for visualization of flow</t>
-  </si>
-  <si>
     <t>Resolve problem in perquisite of the HRR data creation and fetching.</t>
   </si>
   <si>
@@ -291,6 +225,48 @@
   </si>
   <si>
     <t>Scheduled meeting with Director Sir and other stakeholders regarding Nominee application, Asset and Liabilities and Payroll.</t>
+  </si>
+  <si>
+    <t>Project review meeting of IPMS has been done.
+  1. Registration Start Date and End date should be captured.
+  2. CR meeting on 19-11-2025, will be scheduled.
+  3. We are not going to include RPG , right now. It will be discussed later.
+  4. Decision will be gathered from CR about when Project will be finalise i.e when application barred user to modify details. On finalise we will build our master database for future references.</t>
+  </si>
+  <si>
+    <t>IPMS meeting with CR has been done.
+  1. In the detail view, they suggested to show version number along with checker name and date.
+  1. Asked for a non-editable Description field at the time of project initiation.
+  1. They asked for a specific header like Initial Project or Revised Project, along with revision date and approver name, to indicate the project status.
+  1. They have a requirement of trail mail configuration in the application; i.e., when a mail is triggered after the first time, it should contain all previous emails of the project.
+  1. In the next patch, we propose to provide the following:
+  1. Project numbers with post and specialization details entry.
+  2. Assign permanent project numbers.
+  3. Configure email recipients (to whom the email will be triggered).
+  4. Send email for specific mention, if required, to groups or individuals.
+  5. Accommodate user-category-wise login for visualization of flow of data.
+  6. Also try to integrate full project details rendered as view.</t>
+  </si>
+  <si>
+    <t>a. Project Numbers with post and specialization details entry.
+  b. Assign permanent project numbers.
+  c. Configure email, i.e. to whom the email will be triggered.
+  d. Send email to for a specific mention , if required, to specific group of people or individuals.
+  e. We will try to accomodate user category wise login for visualization of flow</t>
+  </si>
+  <si>
+    <t>IPMS meeting with CR was held on 19th Novermebr, 2025. Following points are highlight of the discussion during the presentation.
+  1. In the detail view, they suggested to show version number along with checker name and date.
+  1. Asked for a non-editable Description field at the time of project initiation.
+  1. They asked for a specific header like Initial Project or Revised Project, along with revision date and approver name, to indicate the project status.
+  1. They have a requirement of trail mail configuration in the application; i.e., when a mail is triggered after the first time, it should contain all previous emails of the project.
+  1. In the next patch, we propose to provide the following:
+  1. Project numbers with post and specialization details entry.
+  2. Assign permanent project numbers.
+  3. Configure email recipients (to whom the email will be triggered).
+  4. Send email for specific mention, if required, to groups or individuals.
+  5. Accommodate user-category-wise login for visualization of flow of data.
+  6. Also try to integrate full project details rendered as view.</t>
   </si>
 </sst>
 </file>
@@ -337,10 +313,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -648,7 +627,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -659,7 +638,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -670,7 +649,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -681,7 +660,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -692,7 +671,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -703,7 +682,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -714,7 +693,7 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -725,7 +704,7 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -736,7 +715,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -747,7 +726,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -758,7 +737,7 @@
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -769,7 +748,7 @@
         <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -780,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -791,7 +770,7 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -802,7 +781,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -813,7 +792,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -824,7 +803,7 @@
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -835,7 +814,7 @@
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -846,7 +825,7 @@
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -857,7 +836,7 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1091,15 +1070,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>45975</v>
       </c>
       <c r="B43" t="s">
         <v>9</v>
       </c>
-      <c r="C43" t="s">
-        <v>26</v>
+      <c r="C43" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1110,51 +1089,51 @@
         <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B45" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B46" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B47" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C47" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B48" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1162,7 +1141,7 @@
         <v>45978</v>
       </c>
       <c r="B49" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -1173,106 +1152,106 @@
         <v>45978</v>
       </c>
       <c r="B50" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C50" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B51" t="s">
         <v>3</v>
       </c>
       <c r="C51" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B52" t="s">
         <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B53" t="s">
         <v>3</v>
       </c>
       <c r="C53" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B54" t="s">
         <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B55" t="s">
         <v>3</v>
       </c>
       <c r="C55" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="180" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B56" t="s">
-        <v>3</v>
-      </c>
-      <c r="C56" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B57" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
-        <v>45979</v>
-      </c>
-      <c r="B57" t="s">
-        <v>3</v>
-      </c>
-      <c r="C57" t="s">
-        <v>40</v>
+      <c r="C57" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="B58" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C58" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B59" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C59" t="s">
         <v>37</v>
@@ -1280,608 +1259,240 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="180" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B61" t="s">
         <v>9</v>
       </c>
-      <c r="C61" t="s">
-        <v>45</v>
+      <c r="C61" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B62" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C62" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B63" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C63" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B64" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C64" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B65" t="s">
         <v>9</v>
       </c>
       <c r="C65" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>45980</v>
+        <v>45985</v>
       </c>
       <c r="B66" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C66" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
-        <v>45980</v>
+        <v>45985</v>
       </c>
       <c r="B67" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C67" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>45980</v>
+        <v>45985</v>
       </c>
       <c r="B68" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
-        <v>45980</v>
-      </c>
-      <c r="B69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C69" t="s">
-        <v>53</v>
-      </c>
+      <c r="A69" s="2"/>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
-        <v>45980</v>
-      </c>
-      <c r="B70" t="s">
-        <v>9</v>
-      </c>
-      <c r="C70" t="s">
-        <v>54</v>
-      </c>
+      <c r="A70" s="2"/>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
-        <v>45980</v>
-      </c>
-      <c r="B71" t="s">
-        <v>9</v>
-      </c>
-      <c r="C71" t="s">
-        <v>55</v>
-      </c>
+      <c r="A71" s="2"/>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
-        <v>45980</v>
-      </c>
-      <c r="B72" t="s">
-        <v>56</v>
-      </c>
-      <c r="C72" t="s">
-        <v>82</v>
-      </c>
+      <c r="A72" s="2"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
-        <v>45980</v>
-      </c>
-      <c r="B73" t="s">
-        <v>56</v>
-      </c>
-      <c r="C73" t="s">
-        <v>51</v>
-      </c>
+      <c r="A73" s="2"/>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
-        <v>45980</v>
-      </c>
-      <c r="B74" t="s">
-        <v>56</v>
-      </c>
-      <c r="C74" t="s">
-        <v>83</v>
-      </c>
+      <c r="A74" s="2"/>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
-        <v>45980</v>
-      </c>
-      <c r="B75" t="s">
-        <v>56</v>
-      </c>
-      <c r="C75" t="s">
-        <v>84</v>
-      </c>
+      <c r="A75" s="2"/>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
-        <v>45980</v>
-      </c>
-      <c r="B76" t="s">
-        <v>56</v>
-      </c>
-      <c r="C76" t="s">
-        <v>85</v>
-      </c>
+      <c r="A76" s="2"/>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B77" t="s">
-        <v>3</v>
-      </c>
-      <c r="C77" t="s">
-        <v>41</v>
-      </c>
+      <c r="A77" s="2"/>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B78" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" t="s">
-        <v>42</v>
-      </c>
+      <c r="A78" s="2"/>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B79" t="s">
-        <v>7</v>
-      </c>
-      <c r="C79" t="s">
-        <v>43</v>
-      </c>
+      <c r="A79" s="2"/>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B80" t="s">
-        <v>9</v>
-      </c>
-      <c r="C80" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B81" t="s">
-        <v>9</v>
-      </c>
-      <c r="C81" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B82" t="s">
-        <v>9</v>
-      </c>
-      <c r="C82" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B83" t="s">
-        <v>9</v>
-      </c>
-      <c r="C83" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B84" t="s">
-        <v>9</v>
-      </c>
-      <c r="C84" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B85" t="s">
-        <v>9</v>
-      </c>
-      <c r="C85" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B86" t="s">
-        <v>9</v>
-      </c>
-      <c r="C86" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B87" t="s">
-        <v>9</v>
-      </c>
-      <c r="C87" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B88" t="s">
-        <v>9</v>
-      </c>
-      <c r="C88" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B89" t="s">
-        <v>9</v>
-      </c>
-      <c r="C89" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B90" t="s">
-        <v>9</v>
-      </c>
-      <c r="C90" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B91" t="s">
-        <v>9</v>
-      </c>
-      <c r="C91" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B92" t="s">
-        <v>56</v>
-      </c>
-      <c r="C92" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B93" t="s">
-        <v>3</v>
-      </c>
-      <c r="C93" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B94" t="s">
-        <v>7</v>
-      </c>
-      <c r="C94" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B95" t="s">
-        <v>7</v>
-      </c>
-      <c r="C95" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B96" t="s">
-        <v>9</v>
-      </c>
-      <c r="C96" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B97" t="s">
-        <v>9</v>
-      </c>
-      <c r="C97" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B98" t="s">
-        <v>9</v>
-      </c>
-      <c r="C98" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B99" t="s">
-        <v>9</v>
-      </c>
-      <c r="C99" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B100" t="s">
-        <v>9</v>
-      </c>
-      <c r="C100" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B101" t="s">
-        <v>9</v>
-      </c>
-      <c r="C101" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B102" t="s">
-        <v>9</v>
-      </c>
-      <c r="C102" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B103" t="s">
-        <v>9</v>
-      </c>
-      <c r="C103" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B104" t="s">
-        <v>9</v>
-      </c>
-      <c r="C104" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B105" t="s">
-        <v>9</v>
-      </c>
-      <c r="C105" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B106" t="s">
-        <v>9</v>
-      </c>
-      <c r="C106" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B107" t="s">
-        <v>9</v>
-      </c>
-      <c r="C107" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="2">
-        <v>45981</v>
-      </c>
-      <c r="B108" t="s">
-        <v>56</v>
-      </c>
-      <c r="C108" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="2">
-        <v>45982</v>
-      </c>
-      <c r="B109" t="s">
-        <v>3</v>
-      </c>
-      <c r="C109" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="2">
-        <v>45982</v>
-      </c>
-      <c r="B110" t="s">
-        <v>7</v>
-      </c>
-      <c r="C110" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="2">
-        <v>45982</v>
-      </c>
-      <c r="B111" t="s">
-        <v>9</v>
-      </c>
-      <c r="C111" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="2">
-        <v>45985</v>
-      </c>
-      <c r="B112" t="s">
-        <v>3</v>
-      </c>
-      <c r="C112" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="2">
-        <v>45985</v>
-      </c>
-      <c r="B113" t="s">
-        <v>3</v>
-      </c>
-      <c r="C113" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="2">
-        <v>45985</v>
-      </c>
-      <c r="B114" t="s">
-        <v>7</v>
-      </c>
-      <c r="C114" t="s">
-        <v>60</v>
-      </c>
+      <c r="A80" s="2"/>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="2"/>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2"/>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="2"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2"/>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="2"/>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2"/>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="2"/>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2"/>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="2"/>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="2"/>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="2"/>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2"/>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="2"/>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2"/>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="2"/>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2"/>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="2"/>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2"/>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="2"/>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2"/>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="2"/>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="2"/>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="2"/>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2"/>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="2"/>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="2"/>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="2"/>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="2"/>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="2"/>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2"/>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="2"/>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="2"/>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="2"/>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="73">
   <si>
     <t>Date</t>
   </si>
@@ -267,6 +267,12 @@
   4. Send email for specific mention, if required, to groups or individuals.
   5. Accommodate user-category-wise login for visualization of flow of data.
   6. Also try to integrate full project details rendered as view.</t>
+  </si>
+  <si>
+    <t>Creation of history of project numbers confirmed, postponed and removed.</t>
+  </si>
+  <si>
+    <t>Provide solution for creation of activity of single as well as selected projects to assign project numbers, postpone of a project and deletion of a project.</t>
   </si>
 </sst>
 </file>
@@ -1357,10 +1363,26 @@
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="2"/>
+      <c r="A69" s="2">
+        <v>45986</v>
+      </c>
+      <c r="B69" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="2"/>
+      <c r="A70" s="2">
+        <v>45986</v>
+      </c>
+      <c r="B70" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="74">
   <si>
     <t>Date</t>
   </si>
@@ -273,6 +273,9 @@
   </si>
   <si>
     <t>Provide solution for creation of activity of single as well as selected projects to assign project numbers, postpone of a project and deletion of a project.</t>
+  </si>
+  <si>
+    <t>Working with same Project Number Tab. Alteration of Project number assign part, as Bring post and specialization details to the list for the user to understand for the kaing of decision.</t>
   </si>
 </sst>
 </file>
@@ -1385,7 +1388,15 @@
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="2"/>
+      <c r="A71" s="2">
+        <v>45987</v>
+      </c>
+      <c r="B71" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="75">
   <si>
     <t>Date</t>
   </si>
@@ -276,6 +276,9 @@
   </si>
   <si>
     <t>Working with same Project Number Tab. Alteration of Project number assign part, as Bring post and specialization details to the list for the user to understand for the kaing of decision.</t>
+  </si>
+  <si>
+    <t>Single Project Creation has been done. Working on fixing taken on multiple project number at a time.</t>
   </si>
 </sst>
 </file>
@@ -1399,7 +1402,15 @@
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="2"/>
+      <c r="A72" s="2">
+        <v>45989</v>
+      </c>
+      <c r="B72" t="s">
+        <v>3</v>
+      </c>
+      <c r="C72" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="77">
   <si>
     <t>Date</t>
   </si>
@@ -279,6 +279,17 @@
   </si>
   <si>
     <t>Single Project Creation has been done. Working on fixing taken on multiple project number at a time.</t>
+  </si>
+  <si>
+    <t>Implemented inactivity tracking and Auto sign out after a fixed time. It will increase application security.
+  1. JWT token implementation has been has done in IPMS User App.
+  1. Implementing refresh token generation and validation.</t>
+  </si>
+  <si>
+    <t>Non-editable Description field at the time of project initiation has been implemented.
+  1. Alter table and Procedures.
+  1. Modify project initiation API
+  1. Modify UI and app logic, So that It will integrate with API call.</t>
   </si>
 </sst>
 </file>
@@ -1412,11 +1423,27 @@
         <v>74</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="2"/>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="2"/>
+    <row r="73" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>45993</v>
+      </c>
+      <c r="B73" t="s">
+        <v>3</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>45993</v>
+      </c>
+      <c r="B74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="80">
   <si>
     <t>Date</t>
   </si>
@@ -290,6 +290,15 @@
   1. Alter table and Procedures.
   1. Modify project initiation API
   1. Modify UI and app logic, So that It will integrate with API call.</t>
+  </si>
+  <si>
+    <t>Provide help to Garmia Madam, regarding submission of OD/tour claim</t>
+  </si>
+  <si>
+    <t>Incorporate Retire flag for the HRMS employee count in Division/department list.</t>
+  </si>
+  <si>
+    <t>create view for incometax slab creation.</t>
   </si>
 </sst>
 </file>
@@ -1446,13 +1455,37 @@
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="2"/>
+      <c r="A75" s="2">
+        <v>45994</v>
+      </c>
+      <c r="B75" t="s">
+        <v>3</v>
+      </c>
+      <c r="C75" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="2"/>
+      <c r="A76" s="2">
+        <v>45994</v>
+      </c>
+      <c r="B76" t="s">
+        <v>3</v>
+      </c>
+      <c r="C76" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="2"/>
+      <c r="A77" s="2">
+        <v>45994</v>
+      </c>
+      <c r="B77" t="s">
+        <v>3</v>
+      </c>
+      <c r="C77" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="81">
   <si>
     <t>Date</t>
   </si>
@@ -299,6 +299,9 @@
   </si>
   <si>
     <t>create view for incometax slab creation.</t>
+  </si>
+  <si>
+    <t>Marging of code of two branches, solving conflicts and fixing menu diplay.</t>
   </si>
 </sst>
 </file>
@@ -1488,7 +1491,15 @@
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="2"/>
+      <c r="A78" s="2">
+        <v>45995</v>
+      </c>
+      <c r="B78" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="83">
   <si>
     <t>Date</t>
   </si>
@@ -302,6 +302,12 @@
   </si>
   <si>
     <t>Marging of code of two branches, solving conflicts and fixing menu diplay.</t>
+  </si>
+  <si>
+    <t>Fixed issues of Default Role for an user.</t>
+  </si>
+  <si>
+    <t>Show last revert comment to the maker end.</t>
   </si>
 </sst>
 </file>
@@ -1502,10 +1508,26 @@
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="2"/>
+      <c r="A79" s="2">
+        <v>45999</v>
+      </c>
+      <c r="B79" t="s">
+        <v>3</v>
+      </c>
+      <c r="C79" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="2"/>
+      <c r="A80" s="2">
+        <v>45999</v>
+      </c>
+      <c r="B80" t="s">
+        <v>3</v>
+      </c>
+      <c r="C80" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="84">
   <si>
     <t>Date</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>Show last revert comment to the maker end.</t>
+  </si>
+  <si>
+    <t>Attend Payroll related meeting with accounts.</t>
   </si>
 </sst>
 </file>
@@ -1529,52 +1532,60 @@
         <v>82</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="2"/>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <v>45999</v>
+      </c>
+      <c r="B81" t="s">
+        <v>9</v>
+      </c>
+      <c r="C81" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="90">
   <si>
     <t>Date</t>
   </si>
@@ -311,6 +311,24 @@
   </si>
   <si>
     <t>Attend Payroll related meeting with accounts.</t>
+  </si>
+  <si>
+    <t>Creating Email Configuaration and Send Email</t>
+  </si>
+  <si>
+    <t>need to discuss about automatic email triger point.</t>
+  </si>
+  <si>
+    <t>Email has been configured project wise.</t>
+  </si>
+  <si>
+    <t>Postpone of Project has been done.</t>
+  </si>
+  <si>
+    <t>Before proceding to manage Project Numbers (confirm, postpone, re-open and delete) user have to configure email related to project.</t>
+  </si>
+  <si>
+    <t>Need to discuss with CR about postpone remarks, re-open a project and its effect. also delete and then its effect.</t>
   </si>
 </sst>
 </file>
@@ -1544,22 +1562,70 @@
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="2"/>
+      <c r="A82" s="2">
+        <v>46000</v>
+      </c>
+      <c r="B82" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="2"/>
+      <c r="A83" s="2">
+        <v>46000</v>
+      </c>
+      <c r="B83" t="s">
+        <v>9</v>
+      </c>
+      <c r="C83" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="2"/>
+      <c r="A84" s="2">
+        <v>46001</v>
+      </c>
+      <c r="B84" t="s">
+        <v>3</v>
+      </c>
+      <c r="C84" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="2"/>
+      <c r="A85" s="2">
+        <v>46001</v>
+      </c>
+      <c r="B85" t="s">
+        <v>3</v>
+      </c>
+      <c r="C85" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="2"/>
+      <c r="A86" s="2">
+        <v>46001</v>
+      </c>
+      <c r="B86" t="s">
+        <v>3</v>
+      </c>
+      <c r="C86" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="2"/>
+      <c r="A87" s="2">
+        <v>46001</v>
+      </c>
+      <c r="B87" t="s">
+        <v>39</v>
+      </c>
+      <c r="C87" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="93">
   <si>
     <t>Date</t>
   </si>
@@ -329,6 +329,15 @@
   </si>
   <si>
     <t>Need to discuss with CR about postpone remarks, re-open a project and its effect. also delete and then its effect.</t>
+  </si>
+  <si>
+    <t>An issue is reported regarding extratime allowance mismatch in the weekend period. Find the problem, and resolve the issue.</t>
+  </si>
+  <si>
+    <t>Marge Asset liabilities and Nomination. Fix marge conflicts.</t>
+  </si>
+  <si>
+    <t>Fixing issues for succesful run.</t>
   </si>
 </sst>
 </file>
@@ -1628,13 +1637,37 @@
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="2"/>
+      <c r="A88" s="2">
+        <v>46002</v>
+      </c>
+      <c r="B88" t="s">
+        <v>3</v>
+      </c>
+      <c r="C88" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="2"/>
+      <c r="A89" s="2">
+        <v>46002</v>
+      </c>
+      <c r="B89" t="s">
+        <v>3</v>
+      </c>
+      <c r="C89" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="2"/>
+      <c r="A90" s="2">
+        <v>46002</v>
+      </c>
+      <c r="B90" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="97">
   <si>
     <t>Date</t>
   </si>
@@ -338,6 +338,18 @@
   </si>
   <si>
     <t>Fixing issues for succesful run.</t>
+  </si>
+  <si>
+    <t>New access sytem swipe moment integrated to the HRMS system.</t>
+  </si>
+  <si>
+    <t>Changes suggested By Director sir, regarding OD/TOUR Claim, integrated to the HRMS. He wants Tour approved and any remarks regarding tour approval must be printed in the claim document of OD/Tour. It has been incorporated.</t>
+  </si>
+  <si>
+    <t>Proctoring of PO Exam</t>
+  </si>
+  <si>
+    <t>Training for proctoring of exam</t>
   </si>
 </sst>
 </file>
@@ -1670,16 +1682,48 @@
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="2"/>
+      <c r="A91" s="2">
+        <v>46003</v>
+      </c>
+      <c r="B91" t="s">
+        <v>3</v>
+      </c>
+      <c r="C91" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="2"/>
+      <c r="A92" s="2">
+        <v>46003</v>
+      </c>
+      <c r="B92" t="s">
+        <v>3</v>
+      </c>
+      <c r="C92" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="2"/>
+      <c r="A93" s="2">
+        <v>46003</v>
+      </c>
+      <c r="B93" t="s">
+        <v>3</v>
+      </c>
+      <c r="C93" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="2"/>
+      <c r="A94" s="2">
+        <v>46003</v>
+      </c>
+      <c r="B94" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="102">
   <si>
     <t>Date</t>
   </si>
@@ -350,6 +350,24 @@
   </si>
   <si>
     <t>Training for proctoring of exam</t>
+  </si>
+  <si>
+    <t>Static Layout of Dashboard For All in IPMS incorporated</t>
+  </si>
+  <si>
+    <t>HRMS Publishing Activity
+  1. New attendance configuaration has been marged in attendance system.
+  2. Asset-liabilities and Nomination Module
+  3. OD/Tour Claim documents enhancement, added approved by and date with approval remarks if any.</t>
+  </si>
+  <si>
+    <t>Fixing issue with multiple login from same browser in the IPMS.</t>
+  </si>
+  <si>
+    <t>Fixing consistancy issue in IPMS , ideal time out.</t>
+  </si>
+  <si>
+    <t>Find root cause of a issue raised by HR team , regarding Extra time claim allowances of two similar situation but amount was different.</t>
   </si>
 </sst>
 </file>
@@ -1726,57 +1744,97 @@
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="2"/>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="2"/>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="2"/>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="2"/>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="2"/>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
+        <v>46006</v>
+      </c>
+      <c r="B95" t="s">
+        <v>3</v>
+      </c>
+      <c r="C95" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>46006</v>
+      </c>
+      <c r="B96" t="s">
+        <v>3</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <v>46006</v>
+      </c>
+      <c r="B97" t="s">
+        <v>3</v>
+      </c>
+      <c r="C97" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>46006</v>
+      </c>
+      <c r="B98" t="s">
+        <v>3</v>
+      </c>
+      <c r="C98" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
+        <v>46006</v>
+      </c>
+      <c r="B99" t="s">
+        <v>3</v>
+      </c>
+      <c r="C99" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="118">
   <si>
     <t>Date</t>
   </si>
@@ -375,6 +375,42 @@
   </si>
   <si>
     <t>Working on exam stage and phase creation and modification for drafting purpose.</t>
+  </si>
+  <si>
+    <t>Creating documents for today's IPMS meeting agenda. Preparation for demo of IPMS.</t>
+  </si>
+  <si>
+    <t>Fixation of errors in candidate Category redirection method.</t>
+  </si>
+  <si>
+    <t>Creating to list of Documents and View of content of a document inside IPMS.</t>
+  </si>
+  <si>
+    <t>attend Meeting with CR.</t>
+  </si>
+  <si>
+    <t>Dashboard should consists of critical information. Like Upcoming exam should be There.</t>
+  </si>
+  <si>
+    <t>In dashboard filter should be 7day, 15 day and A month.</t>
+  </si>
+  <si>
+    <t>Email should be triggered with checker in CC.</t>
+  </si>
+  <si>
+    <t>Email triggering to outside domain should be there.</t>
+  </si>
+  <si>
+    <t>Change label of "Category" to "Social Category".</t>
+  </si>
+  <si>
+    <t>Bifurcation needed for social categories.</t>
+  </si>
+  <si>
+    <t>Post postponed option should be provided. CR agreed to reuse the configuration scheme to handle postponded post.</t>
+  </si>
+  <si>
+    <t>Short description should be editable.</t>
   </si>
 </sst>
 </file>
@@ -764,7 +800,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C114"/>
+  <dimension ref="A1:C115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
@@ -1906,59 +1942,136 @@
       </c>
     </row>
     <row r="104" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="4"/>
-      <c r="B104" s="5"/>
-      <c r="C104" s="6"/>
+      <c r="A104" s="4">
+        <v>46008</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="105" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="4"/>
-      <c r="B105" s="5"/>
-      <c r="C105" s="6"/>
+      <c r="A105" s="4">
+        <v>46008</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="106" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="4"/>
-      <c r="B106" s="5"/>
-      <c r="C106" s="6"/>
+      <c r="A106" s="4">
+        <v>46008</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="107" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="4"/>
-      <c r="B107" s="5"/>
-      <c r="C107" s="6"/>
+      <c r="A107" s="4">
+        <v>46008</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="108" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="4"/>
-      <c r="B108" s="5"/>
-      <c r="C108" s="6"/>
+      <c r="A108" s="4">
+        <v>46008</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="109" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="4"/>
-      <c r="B109" s="5"/>
-      <c r="C109" s="6"/>
+      <c r="A109" s="4">
+        <v>46008</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="110" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="4"/>
-      <c r="B110" s="5"/>
-      <c r="C110" s="6"/>
+      <c r="A110" s="4">
+        <v>46008</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="111" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="4"/>
-      <c r="B111" s="5"/>
-      <c r="C111" s="6"/>
+      <c r="A111" s="4">
+        <v>46008</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="112" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="4"/>
-      <c r="B112" s="5"/>
-      <c r="C112" s="6"/>
+      <c r="A112" s="4">
+        <v>46008</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="113" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="4"/>
-      <c r="B113" s="5"/>
-      <c r="C113" s="6"/>
+      <c r="A113" s="4">
+        <v>46008</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="114" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="4"/>
-      <c r="B114" s="5"/>
-      <c r="C114" s="6"/>
+      <c r="A114" s="4">
+        <v>46008</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="8">
+        <v>46008</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C115" s="10" t="s">
+        <v>117</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="119">
   <si>
     <t>Date</t>
   </si>
@@ -411,6 +411,9 @@
   </si>
   <si>
     <t>Short description should be editable.</t>
+  </si>
+  <si>
+    <t>Working on formation of RBAC model. Creation of Authorization filter is going on. Permission set up will done later.</t>
   </si>
 </sst>
 </file>
@@ -800,7 +803,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C115"/>
+  <dimension ref="A1:C116"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
@@ -2073,6 +2076,17 @@
         <v>117</v>
       </c>
     </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="8">
+        <v>46009</v>
+      </c>
+      <c r="B116" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="121">
   <si>
     <t>Date</t>
   </si>
@@ -414,6 +414,12 @@
   </si>
   <si>
     <t>Working on formation of RBAC model. Creation of Authorization filter is going on. Permission set up will done later.</t>
+  </si>
+  <si>
+    <t>Role based authetication on page level hasbeen completed and tested for one Controller.</t>
+  </si>
+  <si>
+    <t>RBAC implementation is going on for the full IPMS APP.</t>
   </si>
 </sst>
 </file>
@@ -803,7 +809,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C116"/>
+  <dimension ref="A1:C118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
@@ -2087,6 +2093,28 @@
         <v>118</v>
       </c>
     </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="8">
+        <v>46010</v>
+      </c>
+      <c r="B117" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C117" s="10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="8">
+        <v>46010</v>
+      </c>
+      <c r="B118" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" s="10" t="s">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="124">
   <si>
     <t>Date</t>
   </si>
@@ -420,6 +420,15 @@
   </si>
   <si>
     <t>RBAC implementation is going on for the full IPMS APP.</t>
+  </si>
+  <si>
+    <t>1. Mr. Satish Narkar was unable to claim is medical reimbursement. Fix the use for time being and enable to make him apply. Also find the root cause of the problem and bring in notice to Tanuja Madam to resolve it permanently.</t>
+  </si>
+  <si>
+    <t>2. When we present demo of IPMS, we found that some fonts file are unable to load due to internet connectivity. resolve the issue by routing all files to the local server.</t>
+  </si>
+  <si>
+    <t>RBAC implementation is created in few controller but testing is pending of those.</t>
   </si>
 </sst>
 </file>
@@ -809,7 +818,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C118"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
@@ -2115,6 +2124,39 @@
         <v>120</v>
       </c>
     </row>
+    <row r="119" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A119" s="8">
+        <v>46013</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C119" s="10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="8">
+        <v>46013</v>
+      </c>
+      <c r="B120" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C120" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="8">
+        <v>46013</v>
+      </c>
+      <c r="B121" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="126">
   <si>
     <t>Date</t>
   </si>
@@ -429,6 +429,12 @@
   </si>
   <si>
     <t>RBAC implementation is created in few controller but testing is pending of those.</t>
+  </si>
+  <si>
+    <t>HRMS Sql Server Job was stopped from 26th December, 2025 night. Correct attandance of all employees from 26th December.</t>
+  </si>
+  <si>
+    <t>HRMS marging and publishing works. Transfer procedures to the production. completed task as requested by Prachi.</t>
   </si>
 </sst>
 </file>
@@ -818,7 +824,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C121"/>
+  <dimension ref="A1:C123"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
@@ -2157,6 +2163,28 @@
         <v>123</v>
       </c>
     </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="8">
+        <v>46020</v>
+      </c>
+      <c r="B122" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C122" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="8">
+        <v>46020</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C123" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="132">
   <si>
     <t>Date</t>
   </si>
@@ -435,6 +435,24 @@
   </si>
   <si>
     <t>HRMS marging and publishing works. Transfer procedures to the production. completed task as requested by Prachi.</t>
+  </si>
+  <si>
+    <t>1. Update column `ExtraAfterStart` of table `tbl_Shifting_scheadule_time_master`. Previously it was same value as `EndTime` . That is why it creates issue when employee has extratime before the shift and they stayed back after shift with less than 30 minutes. Now it is resoled.</t>
+  </si>
+  <si>
+    <t>1. Prachi should modify the screen of shift master entry, with  logic : after shift extratime should be start from shift end time + minimum extratime required (i.e `EndTime + ShiftMinTimeReqdForET`). In the same way Before shift extratime should end will be shift start time - minimum extratime required (i.e `StartTime - ShiftMinTimeReqdForET`).</t>
+  </si>
+  <si>
+    <t>2. Abhik's House rent recovery is not calculated because he's present HRR has been from 16th december , 2025 to 15th december, 2026. When salary has been processed it check if 1st December , 2025 (i.e. 1st day of salary processing month) is fallen between HRR startDate and EndDate, which is clearly out side. That is why his HRR recovery figure has not been updated.</t>
+  </si>
+  <si>
+    <t>3. Also, I spoke to Dishanka about HRR, Then I understood that we must make provision to capture multiple HRR for an employee. Also We should update the calculation logic of HRR recovery.</t>
+  </si>
+  <si>
+    <t>In IPMS, working on Exam phase , penalty exam date and session batch wise storing.</t>
+  </si>
+  <si>
+    <t>IN HRMS, Working on query optimisation of Daily Transaction which took almost 5 to 6 minute in average to complete, Bring it down to 5 sec now. Some More tuning will needed and working on that.</t>
   </si>
 </sst>
 </file>
@@ -824,7 +842,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C123"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
@@ -2185,6 +2203,116 @@
         <v>125</v>
       </c>
     </row>
+    <row r="124" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A124" s="8">
+        <v>46021</v>
+      </c>
+      <c r="B124" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C124" s="10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A125" s="8">
+        <v>46021</v>
+      </c>
+      <c r="B125" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C125" s="10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A126" s="8">
+        <v>46021</v>
+      </c>
+      <c r="B126" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C126" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="8">
+        <v>46021</v>
+      </c>
+      <c r="B127" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C127" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A128" s="8">
+        <v>46022</v>
+      </c>
+      <c r="B128" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C128" s="10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="8">
+        <v>46022</v>
+      </c>
+      <c r="B129" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="8">
+        <v>46022</v>
+      </c>
+      <c r="B130" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A131" s="8">
+        <v>46022</v>
+      </c>
+      <c r="B131" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C131" s="10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A132" s="8">
+        <v>46022</v>
+      </c>
+      <c r="B132" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C132" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="8">
+        <v>46022</v>
+      </c>
+      <c r="B133" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C133" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="137">
   <si>
     <t>Date</t>
   </si>
@@ -453,6 +453,21 @@
   </si>
   <si>
     <t>IN HRMS, Working on query optimisation of Daily Transaction which took almost 5 to 6 minute in average to complete, Bring it down to 5 sec now. Some More tuning will needed and working on that.</t>
+  </si>
+  <si>
+    <t>Going through Document of SDG SOP for ISO auditing.</t>
+  </si>
+  <si>
+    <t>Solve design issue in Nominee of HRMS.</t>
+  </si>
+  <si>
+    <t>Exam Phase deatails Creation API Complete.</t>
+  </si>
+  <si>
+    <t>complete task of Marging of Nominee branch, Resolving conflicts and publishing HRMS</t>
+  </si>
+  <si>
+    <t>Exam phase details App integration from API.</t>
   </si>
 </sst>
 </file>
@@ -842,7 +857,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C133"/>
+  <dimension ref="A1:C138"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
@@ -2313,6 +2328,61 @@
         <v>129</v>
       </c>
     </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="8">
+        <v>46023</v>
+      </c>
+      <c r="B134" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C134" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="8">
+        <v>46023</v>
+      </c>
+      <c r="B135" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C135" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="8">
+        <v>46023</v>
+      </c>
+      <c r="B136" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C136" s="10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="8">
+        <v>46023</v>
+      </c>
+      <c r="B137" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C137" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="8">
+        <v>46023</v>
+      </c>
+      <c r="B138" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" s="10" t="s">
+        <v>136</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="139">
   <si>
     <t>Date</t>
   </si>
@@ -468,6 +468,12 @@
   </si>
   <si>
     <t>Exam phase details App integration from API.</t>
+  </si>
+  <si>
+    <t>Examphase Creation and Updation Process complete. Also It shows in Change log of a Project.</t>
+  </si>
+  <si>
+    <t>There is minor issue on Examphase. After deleting existing exam phase combination , when add new one it did not render with select2.</t>
   </si>
 </sst>
 </file>
@@ -857,7 +863,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C138"/>
+  <dimension ref="A1:C140"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
@@ -2383,6 +2389,28 @@
         <v>136</v>
       </c>
     </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="8">
+        <v>46024</v>
+      </c>
+      <c r="B139" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="8">
+        <v>46024</v>
+      </c>
+      <c r="B140" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C140" s="10" t="s">
+        <v>138</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="144">
   <si>
     <t>Date</t>
   </si>
@@ -474,6 +474,30 @@
   </si>
   <si>
     <t>There is minor issue on Examphase. After deleting existing exam phase combination , when add new one it did not render with select2.</t>
+  </si>
+  <si>
+    <t>Resolve Conflicts, marge and Publish of HRMS code for `asset-liabilities and nominee` in HRMS.</t>
+  </si>
+  <si>
+    <t>Exam phase and test type is sync with database has been complete.</t>
+  </si>
+  <si>
+    <t>Complete of Penalty, Answer choise, exam date entry part
+  1. [x] **Creation of table structure.**
+  2. [x] **Creation of procedure for insert and update.**
+  3. [x] **Creation of Business logic for insertion and updation.**</t>
+  </si>
+  <si>
+    <t>Marge and publish HRMS again.</t>
+  </si>
+  <si>
+    <t>Working on Penalty, Answer choise, exam date entry part
+  1. [ ] **Creation of table structure.**
+  2. [ ] **Creation of procedure for insert and update.**
+  3. [ ] **Plug into the batching process**
+  4. [ ] **Modify the fetch Process**
+  5. [ ] **Creation of API and Business logic for insertion and updation.**
+  6. [ ] **Integrate API to the Application.**</t>
   </si>
 </sst>
 </file>
@@ -863,7 +887,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C140"/>
+  <dimension ref="A1:C145"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
@@ -2411,6 +2435,61 @@
         <v>138</v>
       </c>
     </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="8">
+        <v>46027</v>
+      </c>
+      <c r="B141" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C141" s="10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="8">
+        <v>46027</v>
+      </c>
+      <c r="B142" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C142" s="10" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A143" s="8">
+        <v>46027</v>
+      </c>
+      <c r="B143" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C143" s="10" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="8">
+        <v>46027</v>
+      </c>
+      <c r="B144" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C144" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+      <c r="A145" s="8">
+        <v>46027</v>
+      </c>
+      <c r="B145" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" s="10" t="s">
+        <v>143</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="150">
   <si>
     <t>Date</t>
   </si>
@@ -498,6 +498,26 @@
   4. [ ] **Modify the fetch Process**
   5. [ ] **Creation of API and Business logic for insertion and updation.**
   6. [ ] **Integrate API to the Application.**</t>
+  </si>
+  <si>
+    <t>Marge and Publishing activity of HRMS, for Asset and Nominee changes.</t>
+  </si>
+  <si>
+    <t>2nd Time Marge and Publishing activity of HRMS, for Asset and Nominee changes.</t>
+  </si>
+  <si>
+    <t>Complete of Penalty related Modify the fetch Process</t>
+  </si>
+  <si>
+    <t>Complete of Penalty related Creation of API and Business logic for insertion and updation.</t>
+  </si>
+  <si>
+    <t>Complete of Penalty related Integrate API to the Application.</t>
+  </si>
+  <si>
+    <t>Meeting with CR user Anagha Madam about IPMS Penalty and related services.
+  1. The penalty page should have penalty validation only for exam dates.
+  2. Penalty may be different for different test subjects. So penalty should record there also.</t>
   </si>
 </sst>
 </file>
@@ -887,7 +907,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C145"/>
+  <dimension ref="A1:C151"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
@@ -2490,6 +2510,72 @@
         <v>143</v>
       </c>
     </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="8">
+        <v>46028</v>
+      </c>
+      <c r="B146" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C146" s="10" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="8">
+        <v>46028</v>
+      </c>
+      <c r="B147" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C147" s="10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="8">
+        <v>46028</v>
+      </c>
+      <c r="B148" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C148" s="10" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="8">
+        <v>46028</v>
+      </c>
+      <c r="B149" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C149" s="10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="8">
+        <v>46028</v>
+      </c>
+      <c r="B150" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C150" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A151" s="8">
+        <v>46028</v>
+      </c>
+      <c r="B151" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C151" s="10" t="s">
+        <v>149</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="157">
   <si>
     <t>Date</t>
   </si>
@@ -518,6 +518,27 @@
     <t>Meeting with CR user Anagha Madam about IPMS Penalty and related services.
   1. The penalty page should have penalty validation only for exam dates.
   2. Penalty may be different for different test subjects. So penalty should record there also.</t>
+  </si>
+  <si>
+    <t>Data transfer of Unfairmeans candidate from **`Old server (172.165.10.89)`** to **`New Server (172.165.10.87)`**.</t>
+  </si>
+  <si>
+    <t>For Exam datewise session, Creation of table structure.</t>
+  </si>
+  <si>
+    <t>For Exam datewise session, Creation of procedure for insert and update.</t>
+  </si>
+  <si>
+    <t>For Exam datewise session, Plug into the batching process</t>
+  </si>
+  <si>
+    <t>For Exam datewise session, Modify the fetch Process</t>
+  </si>
+  <si>
+    <t>For Exam datewise session, Creation of API and Business logic for insertion and updation.</t>
+  </si>
+  <si>
+    <t>For Exam datewise session, Integrate API to the Application.</t>
   </si>
 </sst>
 </file>
@@ -907,7 +928,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C151"/>
+  <dimension ref="A1:C158"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
@@ -2576,6 +2597,83 @@
         <v>149</v>
       </c>
     </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="8">
+        <v>46029</v>
+      </c>
+      <c r="B152" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C152" s="10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="8">
+        <v>46029</v>
+      </c>
+      <c r="B153" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C153" s="10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="8">
+        <v>46029</v>
+      </c>
+      <c r="B154" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C154" s="10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="8">
+        <v>46029</v>
+      </c>
+      <c r="B155" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C155" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="8">
+        <v>46029</v>
+      </c>
+      <c r="B156" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C156" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="8">
+        <v>46029</v>
+      </c>
+      <c r="B157" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C157" s="10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="8">
+        <v>46029</v>
+      </c>
+      <c r="B158" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C158" s="10" t="s">
+        <v>156</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="158">
   <si>
     <t>Date</t>
   </si>
@@ -539,6 +539,14 @@
   </si>
   <si>
     <t>For Exam datewise session, Integrate API to the Application.</t>
+  </si>
+  <si>
+    <t>MVP of AdD authnticator application
+  It will Allow a `superadmin` to Register an APP with Username And Password.
+  Upon Successful login of the respective Application Admin , He will see `AppKey` And `AppSecret`. This two will require for Use Authenticator API.
+  Corrosponding Application Admin can view and Generate SecretKey for the Application.
+  To access Authenticate API it needs `Appkey AppSecret EncodedUserName EncodedPassword`
+  We also implemented Versioning of API, API key Retention Policy.</t>
   </si>
 </sst>
 </file>
@@ -928,7 +936,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C158"/>
+  <dimension ref="A1:C159"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
@@ -2674,6 +2682,17 @@
         <v>156</v>
       </c>
     </row>
+    <row r="159" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A159" s="8">
+        <v>46035</v>
+      </c>
+      <c r="B159" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C159" s="10" t="s">
+        <v>157</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="161">
   <si>
     <t>Date</t>
   </si>
@@ -547,6 +547,15 @@
   Corrosponding Application Admin can view and Generate SecretKey for the Application.
   To access Authenticate API it needs `Appkey AppSecret EncodedUserName EncodedPassword`
   We also implemented Versioning of API, API key Retention Policy.</t>
+  </si>
+  <si>
+    <t>Medical Reimbursement claim Issue of Mr. Ashish Shanke has been resolved.</t>
+  </si>
+  <si>
+    <t>AD authetication has been published for trial or UAT purpose.</t>
+  </si>
+  <si>
+    <t>Modify witness alert in Nomination.</t>
   </si>
 </sst>
 </file>
@@ -936,7 +945,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C159"/>
+  <dimension ref="A1:C162"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
@@ -2693,6 +2702,39 @@
         <v>157</v>
       </c>
     </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="8">
+        <v>46069</v>
+      </c>
+      <c r="B160" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C160" s="10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="8">
+        <v>46069</v>
+      </c>
+      <c r="B161" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C161" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="8">
+        <v>46069</v>
+      </c>
+      <c r="B162" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C162" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="166">
   <si>
     <t>Date</t>
   </si>
@@ -556,6 +556,21 @@
   </si>
   <si>
     <t>Modify witness alert in Nomination.</t>
+  </si>
+  <si>
+    <t>1. Result to be shared on captured and display in documents and emails</t>
+  </si>
+  <si>
+    <t>2. Email Communication history has been enbaled to see at any stage of a project life cycle.</t>
+  </si>
+  <si>
+    <t>3. Remove D&amp;A coordinator from emails, also except CR and D&amp;A user no one can view D&amp;A co-ordinators.</t>
+  </si>
+  <si>
+    <t>Post wise candidate count capturing will start. It should capture in Phase wise and post/specialization wise.</t>
+  </si>
+  <si>
+    <t>Did some R and D on select list plugins , for more flexible options.</t>
   </si>
 </sst>
 </file>
@@ -945,7 +960,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C162"/>
+  <dimension ref="A1:C167"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
@@ -2735,6 +2750,61 @@
         <v>160</v>
       </c>
     </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B163" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C163" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B164" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C164" s="10" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B165" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C165" s="10" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B166" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" s="10" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B167" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C167" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="168">
   <si>
     <t>Date</t>
   </si>
@@ -571,6 +571,12 @@
   </si>
   <si>
     <t>Did some R and D on select list plugins , for more flexible options.</t>
+  </si>
+  <si>
+    <t>working on phase wise post/specialization wise candidate count capture.</t>
+  </si>
+  <si>
+    <t>worked on Payroll Module.</t>
   </si>
 </sst>
 </file>
@@ -960,7 +966,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C167"/>
+  <dimension ref="A1:C169"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
@@ -2805,6 +2811,28 @@
         <v>165</v>
       </c>
     </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B168" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B169" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" s="10" t="s">
+        <v>167</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
